--- a/results/components/gene_names/p7s4.xlsx
+++ b/results/components/gene_names/p7s4.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>gene1</t>
   </si>
@@ -22,34 +22,43 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>car</t>
-  </si>
-  <si>
-    <t>Pcaf</t>
-  </si>
-  <si>
-    <t>Mitf</t>
-  </si>
-  <si>
-    <t>mask</t>
-  </si>
-  <si>
-    <t>cin</t>
-  </si>
-  <si>
-    <t>thr</t>
-  </si>
-  <si>
-    <t>ttk</t>
-  </si>
-  <si>
-    <t>ALiX</t>
-  </si>
-  <si>
-    <t>cnc</t>
-  </si>
-  <si>
-    <t>Tak1</t>
+    <t>sgg</t>
+  </si>
+  <si>
+    <t>pot</t>
+  </si>
+  <si>
+    <t>Dif</t>
+  </si>
+  <si>
+    <t>Rca1</t>
+  </si>
+  <si>
+    <t>sas</t>
+  </si>
+  <si>
+    <t>spen</t>
+  </si>
+  <si>
+    <t>lmd</t>
+  </si>
+  <si>
+    <t>gl</t>
+  </si>
+  <si>
+    <t>bon</t>
+  </si>
+  <si>
+    <t>hpo</t>
+  </si>
+  <si>
+    <t>Eip63E</t>
+  </si>
+  <si>
+    <t>abd-A</t>
+  </si>
+  <si>
+    <t>esc</t>
   </si>
 </sst>
 </file>
@@ -381,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -432,6 +441,22 @@
         <v>11</v>
       </c>
     </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/results/components/gene_names/p7s4.xlsx
+++ b/results/components/gene_names/p7s4.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>gene1</t>
   </si>
@@ -22,43 +22,13 @@
     <t>gene2</t>
   </si>
   <si>
-    <t>sgg</t>
-  </si>
-  <si>
-    <t>pot</t>
-  </si>
-  <si>
-    <t>Dif</t>
-  </si>
-  <si>
-    <t>Rca1</t>
-  </si>
-  <si>
-    <t>sas</t>
-  </si>
-  <si>
-    <t>spen</t>
-  </si>
-  <si>
-    <t>lmd</t>
-  </si>
-  <si>
-    <t>gl</t>
-  </si>
-  <si>
-    <t>bon</t>
-  </si>
-  <si>
-    <t>hpo</t>
-  </si>
-  <si>
-    <t>Eip63E</t>
-  </si>
-  <si>
-    <t>abd-A</t>
-  </si>
-  <si>
-    <t>esc</t>
+    <t>kuk</t>
+  </si>
+  <si>
+    <t>neur</t>
+  </si>
+  <si>
+    <t>Rpd3</t>
   </si>
 </sst>
 </file>
@@ -390,7 +360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -414,47 +384,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
